--- a/web/public/forms/chg-naeyeok.xlsx
+++ b/web/public/forms/chg-naeyeok.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설계변경 산출내역서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'설계변경 산출내역서'!$A$1:$X$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.000%;[Red]-0.000%;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.###;[Red]-#,##0.###;&quot;&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.###;[Red]-#,##0.###;0"/>
+    <numFmt numFmtId="168" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +40,48 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +90,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00EEF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +114,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,32 +139,59 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -530,15 +587,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -562,7 +619,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -592,7 +649,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -622,7 +679,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -652,7 +709,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="7" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -682,7 +739,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="7" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -712,7 +769,10 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="8">
+        <f>IF(N(G9)=0,"",G8/G9)</f>
+        <v/>
+      </c>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -733,13 +793,13 @@
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>공종·품명</t>
         </is>
@@ -747,51 +807,51 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>규격</t>
         </is>
       </c>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
       <c r="K12" s="5" t="n"/>
-      <c r="L12" s="7" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>당초수량</t>
         </is>
       </c>
       <c r="M12" s="5" t="n"/>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="9" t="inlineStr">
         <is>
           <t>변경수량</t>
         </is>
       </c>
       <c r="O12" s="5" t="n"/>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="P12" s="9" t="inlineStr">
         <is>
           <t>증감수량</t>
         </is>
       </c>
       <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="7" t="inlineStr">
+      <c r="R12" s="9" t="inlineStr">
         <is>
           <t>적용단가</t>
         </is>
       </c>
       <c r="S12" s="5" t="n"/>
-      <c r="T12" s="7" t="inlineStr">
+      <c r="T12" s="9" t="inlineStr">
         <is>
           <t>증감금액</t>
         </is>
       </c>
       <c r="U12" s="5" t="n"/>
       <c r="V12" s="5" t="n"/>
-      <c r="W12" s="7" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>단가 근거</t>
         </is>
@@ -799,372 +859,456 @@
       <c r="X12" s="5" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
+      <c r="A13" s="10" t="n"/>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr"/>
+      <c r="C13" s="10" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="G13" s="10" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="J13" s="10" t="n"/>
       <c r="K13" s="5" t="n"/>
-      <c r="L13" s="8" t="inlineStr"/>
+      <c r="L13" s="11" t="n"/>
       <c r="M13" s="5" t="n"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="11" t="n"/>
       <c r="O13" s="5" t="n"/>
-      <c r="P13" s="8" t="inlineStr"/>
+      <c r="P13" s="12">
+        <f>IF(AND(L13="",N13=""),"",N(N13)-N(L13))</f>
+        <v/>
+      </c>
       <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="8" t="inlineStr"/>
+      <c r="R13" s="7" t="n"/>
       <c r="S13" s="5" t="n"/>
-      <c r="T13" s="8" t="inlineStr"/>
+      <c r="T13" s="13">
+        <f>IF(OR(P13="",R13=""),"",INT(ROUND(P13*R13,6)))</f>
+        <v/>
+      </c>
       <c r="U13" s="5" t="n"/>
       <c r="V13" s="5" t="n"/>
-      <c r="W13" s="8" t="inlineStr"/>
+      <c r="W13" s="10" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
+      <c r="A14" s="10" t="n"/>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="10" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="8" t="inlineStr"/>
+      <c r="G14" s="10" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
-      <c r="J14" s="8" t="inlineStr"/>
+      <c r="J14" s="10" t="n"/>
       <c r="K14" s="5" t="n"/>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="L14" s="11" t="n"/>
       <c r="M14" s="5" t="n"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="11" t="n"/>
       <c r="O14" s="5" t="n"/>
-      <c r="P14" s="8" t="inlineStr"/>
+      <c r="P14" s="12">
+        <f>IF(AND(L14="",N14=""),"",N(N14)-N(L14))</f>
+        <v/>
+      </c>
       <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="8" t="inlineStr"/>
+      <c r="R14" s="7" t="n"/>
       <c r="S14" s="5" t="n"/>
-      <c r="T14" s="8" t="inlineStr"/>
+      <c r="T14" s="13">
+        <f>IF(OR(P14="",R14=""),"",INT(ROUND(P14*R14,6)))</f>
+        <v/>
+      </c>
       <c r="U14" s="5" t="n"/>
       <c r="V14" s="5" t="n"/>
-      <c r="W14" s="8" t="inlineStr"/>
+      <c r="W14" s="10" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="10" t="n"/>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="8" t="inlineStr"/>
+      <c r="C15" s="10" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="G15" s="10" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
-      <c r="J15" s="8" t="inlineStr"/>
+      <c r="J15" s="10" t="n"/>
       <c r="K15" s="5" t="n"/>
-      <c r="L15" s="8" t="inlineStr"/>
+      <c r="L15" s="11" t="n"/>
       <c r="M15" s="5" t="n"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="11" t="n"/>
       <c r="O15" s="5" t="n"/>
-      <c r="P15" s="8" t="inlineStr"/>
+      <c r="P15" s="12">
+        <f>IF(AND(L15="",N15=""),"",N(N15)-N(L15))</f>
+        <v/>
+      </c>
       <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="8" t="inlineStr"/>
+      <c r="R15" s="7" t="n"/>
       <c r="S15" s="5" t="n"/>
-      <c r="T15" s="8" t="inlineStr"/>
+      <c r="T15" s="13">
+        <f>IF(OR(P15="",R15=""),"",INT(ROUND(P15*R15,6)))</f>
+        <v/>
+      </c>
       <c r="U15" s="5" t="n"/>
       <c r="V15" s="5" t="n"/>
-      <c r="W15" s="8" t="inlineStr"/>
+      <c r="W15" s="10" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="C16" s="10" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="8" t="inlineStr"/>
+      <c r="G16" s="10" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
-      <c r="J16" s="8" t="inlineStr"/>
+      <c r="J16" s="10" t="n"/>
       <c r="K16" s="5" t="n"/>
-      <c r="L16" s="8" t="inlineStr"/>
+      <c r="L16" s="11" t="n"/>
       <c r="M16" s="5" t="n"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="11" t="n"/>
       <c r="O16" s="5" t="n"/>
-      <c r="P16" s="8" t="inlineStr"/>
+      <c r="P16" s="12">
+        <f>IF(AND(L16="",N16=""),"",N(N16)-N(L16))</f>
+        <v/>
+      </c>
       <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="8" t="inlineStr"/>
+      <c r="R16" s="7" t="n"/>
       <c r="S16" s="5" t="n"/>
-      <c r="T16" s="8" t="inlineStr"/>
+      <c r="T16" s="13">
+        <f>IF(OR(P16="",R16=""),"",INT(ROUND(P16*R16,6)))</f>
+        <v/>
+      </c>
       <c r="U16" s="5" t="n"/>
       <c r="V16" s="5" t="n"/>
-      <c r="W16" s="8" t="inlineStr"/>
+      <c r="W16" s="10" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr"/>
+      <c r="A17" s="10" t="n"/>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="8" t="inlineStr"/>
+      <c r="C17" s="10" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="8" t="inlineStr"/>
+      <c r="G17" s="10" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
-      <c r="J17" s="8" t="inlineStr"/>
+      <c r="J17" s="10" t="n"/>
       <c r="K17" s="5" t="n"/>
-      <c r="L17" s="8" t="inlineStr"/>
+      <c r="L17" s="11" t="n"/>
       <c r="M17" s="5" t="n"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="11" t="n"/>
       <c r="O17" s="5" t="n"/>
-      <c r="P17" s="8" t="inlineStr"/>
+      <c r="P17" s="12">
+        <f>IF(AND(L17="",N17=""),"",N(N17)-N(L17))</f>
+        <v/>
+      </c>
       <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="8" t="inlineStr"/>
+      <c r="R17" s="7" t="n"/>
       <c r="S17" s="5" t="n"/>
-      <c r="T17" s="8" t="inlineStr"/>
+      <c r="T17" s="13">
+        <f>IF(OR(P17="",R17=""),"",INT(ROUND(P17*R17,6)))</f>
+        <v/>
+      </c>
       <c r="U17" s="5" t="n"/>
       <c r="V17" s="5" t="n"/>
-      <c r="W17" s="8" t="inlineStr"/>
+      <c r="W17" s="10" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr"/>
+      <c r="A18" s="10" t="n"/>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C18" s="10" t="n"/>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="8" t="inlineStr"/>
+      <c r="G18" s="10" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
-      <c r="J18" s="8" t="inlineStr"/>
+      <c r="J18" s="10" t="n"/>
       <c r="K18" s="5" t="n"/>
-      <c r="L18" s="8" t="inlineStr"/>
+      <c r="L18" s="11" t="n"/>
       <c r="M18" s="5" t="n"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="11" t="n"/>
       <c r="O18" s="5" t="n"/>
-      <c r="P18" s="8" t="inlineStr"/>
+      <c r="P18" s="12">
+        <f>IF(AND(L18="",N18=""),"",N(N18)-N(L18))</f>
+        <v/>
+      </c>
       <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="8" t="inlineStr"/>
+      <c r="R18" s="7" t="n"/>
       <c r="S18" s="5" t="n"/>
-      <c r="T18" s="8" t="inlineStr"/>
+      <c r="T18" s="13">
+        <f>IF(OR(P18="",R18=""),"",INT(ROUND(P18*R18,6)))</f>
+        <v/>
+      </c>
       <c r="U18" s="5" t="n"/>
       <c r="V18" s="5" t="n"/>
-      <c r="W18" s="8" t="inlineStr"/>
+      <c r="W18" s="10" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr"/>
+      <c r="A19" s="10" t="n"/>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="8" t="inlineStr"/>
+      <c r="C19" s="10" t="n"/>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="8" t="inlineStr"/>
+      <c r="G19" s="10" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
-      <c r="J19" s="8" t="inlineStr"/>
+      <c r="J19" s="10" t="n"/>
       <c r="K19" s="5" t="n"/>
-      <c r="L19" s="8" t="inlineStr"/>
+      <c r="L19" s="11" t="n"/>
       <c r="M19" s="5" t="n"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="11" t="n"/>
       <c r="O19" s="5" t="n"/>
-      <c r="P19" s="8" t="inlineStr"/>
+      <c r="P19" s="12">
+        <f>IF(AND(L19="",N19=""),"",N(N19)-N(L19))</f>
+        <v/>
+      </c>
       <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="8" t="inlineStr"/>
+      <c r="R19" s="7" t="n"/>
       <c r="S19" s="5" t="n"/>
-      <c r="T19" s="8" t="inlineStr"/>
+      <c r="T19" s="13">
+        <f>IF(OR(P19="",R19=""),"",INT(ROUND(P19*R19,6)))</f>
+        <v/>
+      </c>
       <c r="U19" s="5" t="n"/>
       <c r="V19" s="5" t="n"/>
-      <c r="W19" s="8" t="inlineStr"/>
+      <c r="W19" s="10" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr"/>
+      <c r="A20" s="10" t="n"/>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="10" t="n"/>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="8" t="inlineStr"/>
+      <c r="G20" s="10" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
-      <c r="J20" s="8" t="inlineStr"/>
+      <c r="J20" s="10" t="n"/>
       <c r="K20" s="5" t="n"/>
-      <c r="L20" s="8" t="inlineStr"/>
+      <c r="L20" s="11" t="n"/>
       <c r="M20" s="5" t="n"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="11" t="n"/>
       <c r="O20" s="5" t="n"/>
-      <c r="P20" s="8" t="inlineStr"/>
+      <c r="P20" s="12">
+        <f>IF(AND(L20="",N20=""),"",N(N20)-N(L20))</f>
+        <v/>
+      </c>
       <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="8" t="inlineStr"/>
+      <c r="R20" s="7" t="n"/>
       <c r="S20" s="5" t="n"/>
-      <c r="T20" s="8" t="inlineStr"/>
+      <c r="T20" s="13">
+        <f>IF(OR(P20="",R20=""),"",INT(ROUND(P20*R20,6)))</f>
+        <v/>
+      </c>
       <c r="U20" s="5" t="n"/>
       <c r="V20" s="5" t="n"/>
-      <c r="W20" s="8" t="inlineStr"/>
+      <c r="W20" s="10" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr"/>
+      <c r="A21" s="10" t="n"/>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="8" t="inlineStr"/>
+      <c r="C21" s="10" t="n"/>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="8" t="inlineStr"/>
+      <c r="G21" s="10" t="n"/>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
-      <c r="J21" s="8" t="inlineStr"/>
+      <c r="J21" s="10" t="n"/>
       <c r="K21" s="5" t="n"/>
-      <c r="L21" s="8" t="inlineStr"/>
+      <c r="L21" s="11" t="n"/>
       <c r="M21" s="5" t="n"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="11" t="n"/>
       <c r="O21" s="5" t="n"/>
-      <c r="P21" s="8" t="inlineStr"/>
+      <c r="P21" s="12">
+        <f>IF(AND(L21="",N21=""),"",N(N21)-N(L21))</f>
+        <v/>
+      </c>
       <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="8" t="inlineStr"/>
+      <c r="R21" s="7" t="n"/>
       <c r="S21" s="5" t="n"/>
-      <c r="T21" s="8" t="inlineStr"/>
+      <c r="T21" s="13">
+        <f>IF(OR(P21="",R21=""),"",INT(ROUND(P21*R21,6)))</f>
+        <v/>
+      </c>
       <c r="U21" s="5" t="n"/>
       <c r="V21" s="5" t="n"/>
-      <c r="W21" s="8" t="inlineStr"/>
+      <c r="W21" s="10" t="n"/>
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr"/>
+      <c r="A22" s="10" t="n"/>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="8" t="inlineStr"/>
+      <c r="C22" s="10" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="8" t="inlineStr"/>
+      <c r="G22" s="10" t="n"/>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
-      <c r="J22" s="8" t="inlineStr"/>
+      <c r="J22" s="10" t="n"/>
       <c r="K22" s="5" t="n"/>
-      <c r="L22" s="8" t="inlineStr"/>
+      <c r="L22" s="11" t="n"/>
       <c r="M22" s="5" t="n"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="11" t="n"/>
       <c r="O22" s="5" t="n"/>
-      <c r="P22" s="8" t="inlineStr"/>
+      <c r="P22" s="12">
+        <f>IF(AND(L22="",N22=""),"",N(N22)-N(L22))</f>
+        <v/>
+      </c>
       <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="8" t="inlineStr"/>
+      <c r="R22" s="7" t="n"/>
       <c r="S22" s="5" t="n"/>
-      <c r="T22" s="8" t="inlineStr"/>
+      <c r="T22" s="13">
+        <f>IF(OR(P22="",R22=""),"",INT(ROUND(P22*R22,6)))</f>
+        <v/>
+      </c>
       <c r="U22" s="5" t="n"/>
       <c r="V22" s="5" t="n"/>
-      <c r="W22" s="8" t="inlineStr"/>
+      <c r="W22" s="10" t="n"/>
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="8" t="inlineStr"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="5" t="n"/>
-      <c r="C23" s="8" t="inlineStr"/>
+      <c r="C23" s="10" t="n"/>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="8" t="inlineStr"/>
+      <c r="G23" s="10" t="n"/>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="n"/>
-      <c r="J23" s="8" t="inlineStr"/>
+      <c r="J23" s="10" t="n"/>
       <c r="K23" s="5" t="n"/>
-      <c r="L23" s="8" t="inlineStr"/>
+      <c r="L23" s="11" t="n"/>
       <c r="M23" s="5" t="n"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="11" t="n"/>
       <c r="O23" s="5" t="n"/>
-      <c r="P23" s="8" t="inlineStr"/>
+      <c r="P23" s="12">
+        <f>IF(AND(L23="",N23=""),"",N(N23)-N(L23))</f>
+        <v/>
+      </c>
       <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="8" t="inlineStr"/>
+      <c r="R23" s="7" t="n"/>
       <c r="S23" s="5" t="n"/>
-      <c r="T23" s="8" t="inlineStr"/>
+      <c r="T23" s="13">
+        <f>IF(OR(P23="",R23=""),"",INT(ROUND(P23*R23,6)))</f>
+        <v/>
+      </c>
       <c r="U23" s="5" t="n"/>
       <c r="V23" s="5" t="n"/>
-      <c r="W23" s="8" t="inlineStr"/>
+      <c r="W23" s="10" t="n"/>
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr"/>
+      <c r="A24" s="10" t="n"/>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="8" t="inlineStr"/>
+      <c r="C24" s="10" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="8" t="inlineStr"/>
+      <c r="G24" s="10" t="n"/>
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
-      <c r="J24" s="8" t="inlineStr"/>
+      <c r="J24" s="10" t="n"/>
       <c r="K24" s="5" t="n"/>
-      <c r="L24" s="8" t="inlineStr"/>
+      <c r="L24" s="11" t="n"/>
       <c r="M24" s="5" t="n"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="11" t="n"/>
       <c r="O24" s="5" t="n"/>
-      <c r="P24" s="8" t="inlineStr"/>
+      <c r="P24" s="12">
+        <f>IF(AND(L24="",N24=""),"",N(N24)-N(L24))</f>
+        <v/>
+      </c>
       <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="8" t="inlineStr"/>
+      <c r="R24" s="7" t="n"/>
       <c r="S24" s="5" t="n"/>
-      <c r="T24" s="8" t="inlineStr"/>
+      <c r="T24" s="13">
+        <f>IF(OR(P24="",R24=""),"",INT(ROUND(P24*R24,6)))</f>
+        <v/>
+      </c>
       <c r="U24" s="5" t="n"/>
       <c r="V24" s="5" t="n"/>
-      <c r="W24" s="8" t="inlineStr"/>
+      <c r="W24" s="10" t="n"/>
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="8" t="inlineStr"/>
+      <c r="A25" s="10" t="n"/>
       <c r="B25" s="5" t="n"/>
-      <c r="C25" s="8" t="inlineStr"/>
+      <c r="C25" s="10" t="n"/>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="8" t="inlineStr"/>
+      <c r="G25" s="10" t="n"/>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
-      <c r="J25" s="8" t="inlineStr"/>
+      <c r="J25" s="10" t="n"/>
       <c r="K25" s="5" t="n"/>
-      <c r="L25" s="8" t="inlineStr"/>
+      <c r="L25" s="11" t="n"/>
       <c r="M25" s="5" t="n"/>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="11" t="n"/>
       <c r="O25" s="5" t="n"/>
-      <c r="P25" s="8" t="inlineStr"/>
+      <c r="P25" s="12">
+        <f>IF(AND(L25="",N25=""),"",N(N25)-N(L25))</f>
+        <v/>
+      </c>
       <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="8" t="inlineStr"/>
+      <c r="R25" s="7" t="n"/>
       <c r="S25" s="5" t="n"/>
-      <c r="T25" s="8" t="inlineStr"/>
+      <c r="T25" s="13">
+        <f>IF(OR(P25="",R25=""),"",INT(ROUND(P25*R25,6)))</f>
+        <v/>
+      </c>
       <c r="U25" s="5" t="n"/>
       <c r="V25" s="5" t="n"/>
-      <c r="W25" s="8" t="inlineStr"/>
+      <c r="W25" s="10" t="n"/>
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="inlineStr"/>
+      <c r="A26" s="10" t="n"/>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="8" t="inlineStr"/>
+      <c r="C26" s="10" t="n"/>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="8" t="inlineStr"/>
+      <c r="G26" s="10" t="n"/>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
-      <c r="J26" s="8" t="inlineStr"/>
+      <c r="J26" s="10" t="n"/>
       <c r="K26" s="5" t="n"/>
-      <c r="L26" s="8" t="inlineStr"/>
+      <c r="L26" s="11" t="n"/>
       <c r="M26" s="5" t="n"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="11" t="n"/>
       <c r="O26" s="5" t="n"/>
-      <c r="P26" s="8" t="inlineStr"/>
+      <c r="P26" s="12">
+        <f>IF(AND(L26="",N26=""),"",N(N26)-N(L26))</f>
+        <v/>
+      </c>
       <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="8" t="inlineStr"/>
+      <c r="R26" s="7" t="n"/>
       <c r="S26" s="5" t="n"/>
-      <c r="T26" s="8" t="inlineStr"/>
+      <c r="T26" s="13">
+        <f>IF(OR(P26="",R26=""),"",INT(ROUND(P26*R26,6)))</f>
+        <v/>
+      </c>
       <c r="U26" s="5" t="n"/>
       <c r="V26" s="5" t="n"/>
-      <c r="W26" s="8" t="inlineStr"/>
+      <c r="W26" s="10" t="n"/>
       <c r="X26" s="5" t="n"/>
     </row>
     <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>※ 구분: 증가(계약단가) / 감소(계약단가) / 신규(설계변경 당시 단가 × 낙찰률) / 협의(발주기관 요구)</t>
         </is>
@@ -1182,7 +1326,10 @@
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="6" t="inlineStr"/>
+      <c r="G30" s="13">
+        <f>SUMIF(T13:T26,"&gt;0")</f>
+        <v/>
+      </c>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
@@ -1212,7 +1359,10 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="6" t="inlineStr"/>
+      <c r="G31" s="13">
+        <f>SUMIF(T13:T26,"&lt;0")</f>
+        <v/>
+      </c>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
@@ -1242,7 +1392,10 @@
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
-      <c r="G32" s="6" t="inlineStr"/>
+      <c r="G32" s="13">
+        <f>SUM(T13:T26)</f>
+        <v/>
+      </c>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
@@ -1272,7 +1425,7 @@
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
-      <c r="G33" s="6" t="inlineStr"/>
+      <c r="G33" s="7" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
@@ -1294,46 +1447,64 @@
     <row r="34" ht="6" customHeight="1"/>
     <row r="35" ht="10" customHeight="1"/>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="K37" s="11" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="16" t="inlineStr"/>
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="Q37" s="18" t="n"/>
+      <c r="U37" s="19" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="K38" s="11" t="inlineStr">
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="16" t="inlineStr"/>
+      <c r="K38" s="17" t="inlineStr">
         <is>
           <t>대표자</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="Q38" s="18" t="n"/>
+      <c r="U38" s="19" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>증감 금액은 직접공사비입니다. 제경비·일반관리비·이윤·부가세를 붙인 «변경 후 계약금액» 은 공사원가계산서 서식으로 산출해 적으세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="180">
+  <mergeCells count="186">
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="N20:O20"/>
@@ -1345,6 +1516,7 @@
     <mergeCell ref="W24:X24"/>
     <mergeCell ref="L19:M19"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="U38:X38"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="P22:Q22"/>
     <mergeCell ref="C13:F13"/>
@@ -1362,6 +1534,7 @@
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="N14:O14"/>
     <mergeCell ref="R12:S12"/>
+    <mergeCell ref="K38:P38"/>
     <mergeCell ref="G16:I16"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="A31:F31"/>
@@ -1377,7 +1550,6 @@
     <mergeCell ref="P15:Q15"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="N24:O24"/>
-    <mergeCell ref="K38:R38"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="W14:X14"/>
     <mergeCell ref="R18:S18"/>
@@ -1393,6 +1565,7 @@
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="R19:S19"/>
     <mergeCell ref="T26:V26"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="R16:S16"/>
@@ -1401,12 +1574,14 @@
     <mergeCell ref="G33:X33"/>
     <mergeCell ref="A42:X42"/>
     <mergeCell ref="T17:V17"/>
+    <mergeCell ref="Q37:T37"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="J20:K20"/>
     <mergeCell ref="W16:X16"/>
     <mergeCell ref="T19:V19"/>
     <mergeCell ref="L20:M20"/>
+    <mergeCell ref="K37:P37"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A28:X28"/>
     <mergeCell ref="G8:X8"/>
@@ -1416,6 +1591,7 @@
     <mergeCell ref="N13:O13"/>
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="Q38:T38"/>
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="W17:X17"/>
     <mergeCell ref="P14:Q14"/>
@@ -1423,9 +1599,9 @@
     <mergeCell ref="R14:S14"/>
     <mergeCell ref="W19:X19"/>
     <mergeCell ref="R23:S23"/>
-    <mergeCell ref="S38:X38"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="W25:X25"/>
+    <mergeCell ref="A41:X41"/>
     <mergeCell ref="T12:V12"/>
     <mergeCell ref="T21:V21"/>
     <mergeCell ref="C18:F18"/>
@@ -1466,15 +1642,1279 @@
     <mergeCell ref="R22:S22"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="U37:X37"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="G23:I23"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="K37:R37"/>
     <mergeCell ref="T25:V25"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="J14:K14"/>
-    <mergeCell ref="S37:X37"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="G30:X30"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="A43:X43"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="G32:X32"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="A36:X36"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="J17:K17"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="A13 A14 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"증가,감소,신규,협의"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>설계변경 산출내역서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  계약번호</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>제2026-0312호</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  변경 차수</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>제1회</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  계약금액</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="7" t="n">
+        <v>963241000</v>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  예정가격</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="7" t="n">
+        <v>1101487000</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  낙 찰 률</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="8">
+        <f>IF(N(G9)=0,"",G8/G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="6" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>공종·품명</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>당초수량</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>변경수량</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>증감수량</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>적용단가</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="9" t="inlineStr">
+        <is>
+          <t>증감금액</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>단가 근거</t>
+        </is>
+      </c>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>증가</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>PE 이중벽관</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>D600</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="11" t="n">
+        <v>820</v>
+      </c>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="11" t="n">
+        <v>862</v>
+      </c>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="12">
+        <f>IF(AND(L13="",N13=""),"",N(N13)-N(L13))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="7" t="n">
+        <v>163090</v>
+      </c>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="13">
+        <f>IF(OR(P13="",R13=""),"",INT(ROUND(P13*R13,6)))</f>
+        <v/>
+      </c>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="10" t="inlineStr">
+        <is>
+          <t>계약단가</t>
+        </is>
+      </c>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>감소</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>아스팔트 포장(표층)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>t=5cm</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="11" t="n">
+        <v>6300</v>
+      </c>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="11" t="n">
+        <v>6020</v>
+      </c>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="12">
+        <f>IF(AND(L14="",N14=""),"",N(N14)-N(L14))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="7" t="n">
+        <v>12480</v>
+      </c>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="13">
+        <f>IF(OR(P14="",R14=""),"",INT(ROUND(P14*R14,6)))</f>
+        <v/>
+      </c>
+      <c r="U14" s="5" t="n"/>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="10" t="inlineStr">
+        <is>
+          <t>계약단가</t>
+        </is>
+      </c>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>집수정</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>1.2×1.2</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="12">
+        <f>IF(AND(L15="",N15=""),"",N(N15)-N(L15))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="7" t="n">
+        <v>1088777</v>
+      </c>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="13">
+        <f>IF(OR(P15="",R15=""),"",INT(ROUND(P15*R15,6)))</f>
+        <v/>
+      </c>
+      <c r="U15" s="5" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>당시단가×낙찰률</t>
+        </is>
+      </c>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>협의</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>가물막이(톤마대)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>1톤</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="12">
+        <f>IF(AND(L16="",N16=""),"",N(N16)-N(L16))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="7" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="13">
+        <f>IF(OR(P16="",R16=""),"",INT(ROUND(P16*R16,6)))</f>
+        <v/>
+      </c>
+      <c r="U16" s="5" t="n"/>
+      <c r="V16" s="5" t="n"/>
+      <c r="W16" s="10" t="inlineStr">
+        <is>
+          <t>협의</t>
+        </is>
+      </c>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="11" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="12">
+        <f>IF(AND(L17="",N17=""),"",N(N17)-N(L17))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="7" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="13">
+        <f>IF(OR(P17="",R17=""),"",INT(ROUND(P17*R17,6)))</f>
+        <v/>
+      </c>
+      <c r="U17" s="5" t="n"/>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="11" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="11" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="12">
+        <f>IF(AND(L18="",N18=""),"",N(N18)-N(L18))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="13">
+        <f>IF(OR(P18="",R18=""),"",INT(ROUND(P18*R18,6)))</f>
+        <v/>
+      </c>
+      <c r="U18" s="5" t="n"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="12">
+        <f>IF(AND(L19="",N19=""),"",N(N19)-N(L19))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="7" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="13">
+        <f>IF(OR(P19="",R19=""),"",INT(ROUND(P19*R19,6)))</f>
+        <v/>
+      </c>
+      <c r="U19" s="5" t="n"/>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="11" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="12">
+        <f>IF(AND(L20="",N20=""),"",N(N20)-N(L20))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="7" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="13">
+        <f>IF(OR(P20="",R20=""),"",INT(ROUND(P20*R20,6)))</f>
+        <v/>
+      </c>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="10" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="12">
+        <f>IF(AND(L21="",N21=""),"",N(N21)-N(L21))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="7" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="13">
+        <f>IF(OR(P21="",R21=""),"",INT(ROUND(P21*R21,6)))</f>
+        <v/>
+      </c>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="11" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="12">
+        <f>IF(AND(L22="",N22=""),"",N(N22)-N(L22))</f>
+        <v/>
+      </c>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="7" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="13">
+        <f>IF(OR(P22="",R22=""),"",INT(ROUND(P22*R22,6)))</f>
+        <v/>
+      </c>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="10" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="12">
+        <f>IF(AND(L23="",N23=""),"",N(N23)-N(L23))</f>
+        <v/>
+      </c>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="7" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="13">
+        <f>IF(OR(P23="",R23=""),"",INT(ROUND(P23*R23,6)))</f>
+        <v/>
+      </c>
+      <c r="U23" s="5" t="n"/>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="10" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="11" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="12">
+        <f>IF(AND(L24="",N24=""),"",N(N24)-N(L24))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="7" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="13">
+        <f>IF(OR(P24="",R24=""),"",INT(ROUND(P24*R24,6)))</f>
+        <v/>
+      </c>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="12">
+        <f>IF(AND(L25="",N25=""),"",N(N25)-N(L25))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="7" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="13">
+        <f>IF(OR(P25="",R25=""),"",INT(ROUND(P25*R25,6)))</f>
+        <v/>
+      </c>
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="11" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="12">
+        <f>IF(AND(L26="",N26=""),"",N(N26)-N(L26))</f>
+        <v/>
+      </c>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="7" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="13">
+        <f>IF(OR(P26="",R26=""),"",INT(ROUND(P26*R26,6)))</f>
+        <v/>
+      </c>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="10" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="6" customHeight="1"/>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>※ 구분: 증가(계약단가) / 감소(계약단가) / 신규(설계변경 당시 단가 × 낙찰률) / 협의(발주기관 요구)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  증가 소계</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="13">
+        <f>SUMIF(T13:T26,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" s="5" t="n"/>
+      <c r="T30" s="5" t="n"/>
+      <c r="U30" s="5" t="n"/>
+      <c r="V30" s="5" t="n"/>
+      <c r="W30" s="5" t="n"/>
+      <c r="X30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  감소 소계</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="13">
+        <f>SUMIF(T13:T26,"&lt;0")</f>
+        <v/>
+      </c>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
+      <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" s="5" t="n"/>
+      <c r="T31" s="5" t="n"/>
+      <c r="U31" s="5" t="n"/>
+      <c r="V31" s="5" t="n"/>
+      <c r="W31" s="5" t="n"/>
+      <c r="X31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  증감 합계</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="13">
+        <f>SUM(T13:T26)</f>
+        <v/>
+      </c>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+      <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="5" t="n"/>
+      <c r="T32" s="5" t="n"/>
+      <c r="U32" s="5" t="n"/>
+      <c r="V32" s="5" t="n"/>
+      <c r="W32" s="5" t="n"/>
+      <c r="X32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  변경 후 계약금액</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="7" t="n">
+        <v>1011891000</v>
+      </c>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+      <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="5" t="n"/>
+      <c r="T33" s="5" t="n"/>
+      <c r="U33" s="5" t="n"/>
+      <c r="V33" s="5" t="n"/>
+      <c r="W33" s="5" t="n"/>
+      <c r="X33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35" ht="10" customHeight="1"/>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="15" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="16" t="inlineStr"/>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q37" s="18" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U37" s="19" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="16" t="inlineStr"/>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>대표자</t>
+        </is>
+      </c>
+      <c r="Q38" s="18" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="U38" s="19" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="6" customHeight="1"/>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="184">
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="G10:X10"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="U38:X38"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="T22:V22"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="K38:P38"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="G31:X31"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="T20:V20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="T26:V26"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="G33:X33"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="T19:V19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="K37:P37"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A28:X28"/>
+    <mergeCell ref="G8:X8"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="Q38:T38"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="A41:X41"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="T21:V21"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="T23:V23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="W21:X21"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="J14:K14"/>
     <mergeCell ref="G18:I18"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="R13:S13"/>
@@ -1505,6 +2945,7 @@
     <mergeCell ref="T24:V24"/>
     <mergeCell ref="P18:Q18"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A37:J37"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="A6:F6"/>
@@ -1515,7 +2956,13 @@
     <mergeCell ref="W13:X13"/>
     <mergeCell ref="J17:K17"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="A13 A14 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"증가,감소,신규,협의"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/chg-naeyeok.xlsx
+++ b/web/public/forms/chg-naeyeok.xlsx
@@ -197,6 +197,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="300" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="301" formatCode="#,##0;[Red]-#,##0;0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1692,6 +1700,21 @@
     <mergeCell ref="W13:X13"/>
     <mergeCell ref="J17:K17"/>
   </mergeCells>
+  <conditionalFormatting sqref="L13:L26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(L13),MOD(L13,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13:N26">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(ISNUMBER(N13),MOD(N13,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P13:P26">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>AND(ISNUMBER(P13),MOD(P13,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="A13 A14 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
       <formula1>"증가,감소,신규,협의"</formula1>
@@ -2026,7 +2049,7 @@
       </c>
       <c r="X12" s="5" t="n"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>증가</t>
@@ -2084,7 +2107,7 @@
       </c>
       <c r="X13" s="5" t="n"/>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>감소</t>
@@ -2142,7 +2165,7 @@
       </c>
       <c r="X14" s="5" t="n"/>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>신규</t>
@@ -2200,7 +2223,7 @@
       </c>
       <c r="X15" s="5" t="n"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>협의</t>
@@ -2956,6 +2979,21 @@
     <mergeCell ref="W13:X13"/>
     <mergeCell ref="J17:K17"/>
   </mergeCells>
+  <conditionalFormatting sqref="L13:L26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(ISNUMBER(L13),MOD(L13,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13:N26">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(ISNUMBER(N13),MOD(N13,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P13:P26">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>AND(ISNUMBER(P13),MOD(P13,1)=0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="A13 A14 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
       <formula1>"증가,감소,신규,협의"</formula1>

--- a/web/public/forms/chg-naeyeok.xlsx
+++ b/web/public/forms/chg-naeyeok.xlsx
@@ -598,7 +598,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="21" t="inlineStr">

--- a/web/public/forms/chg-naeyeok.xlsx
+++ b/web/public/forms/chg-naeyeok.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설계변경 산출내역서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'설계변경 산출내역서'!$A$1:$X$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -130,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -189,22 +187,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <numFmt numFmtId="300" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="301" formatCode="#,##0;[Red]-#,##0;0"/>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -777,10 +764,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="8">
-        <f>IF(N(G9)=0,"",G8/G9)</f>
-        <v/>
-      </c>
+      <c r="G10" s="8" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -882,17 +866,11 @@
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="5" t="n"/>
-      <c r="P13" s="12">
-        <f>IF(AND(L13="",N13=""),"",N(N13)-N(L13))</f>
-        <v/>
-      </c>
+      <c r="P13" s="12" t="n"/>
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="7" t="n"/>
       <c r="S13" s="5" t="n"/>
-      <c r="T13" s="13">
-        <f>IF(OR(P13="",R13=""),"",INT(ROUND(P13*R13,6)))</f>
-        <v/>
-      </c>
+      <c r="T13" s="13" t="n"/>
       <c r="U13" s="5" t="n"/>
       <c r="V13" s="5" t="n"/>
       <c r="W13" s="10" t="n"/>
@@ -914,17 +892,11 @@
       <c r="M14" s="5" t="n"/>
       <c r="N14" s="11" t="n"/>
       <c r="O14" s="5" t="n"/>
-      <c r="P14" s="12">
-        <f>IF(AND(L14="",N14=""),"",N(N14)-N(L14))</f>
-        <v/>
-      </c>
+      <c r="P14" s="12" t="n"/>
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="7" t="n"/>
       <c r="S14" s="5" t="n"/>
-      <c r="T14" s="13">
-        <f>IF(OR(P14="",R14=""),"",INT(ROUND(P14*R14,6)))</f>
-        <v/>
-      </c>
+      <c r="T14" s="13" t="n"/>
       <c r="U14" s="5" t="n"/>
       <c r="V14" s="5" t="n"/>
       <c r="W14" s="10" t="n"/>
@@ -946,17 +918,11 @@
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="11" t="n"/>
       <c r="O15" s="5" t="n"/>
-      <c r="P15" s="12">
-        <f>IF(AND(L15="",N15=""),"",N(N15)-N(L15))</f>
-        <v/>
-      </c>
+      <c r="P15" s="12" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="7" t="n"/>
       <c r="S15" s="5" t="n"/>
-      <c r="T15" s="13">
-        <f>IF(OR(P15="",R15=""),"",INT(ROUND(P15*R15,6)))</f>
-        <v/>
-      </c>
+      <c r="T15" s="13" t="n"/>
       <c r="U15" s="5" t="n"/>
       <c r="V15" s="5" t="n"/>
       <c r="W15" s="10" t="n"/>
@@ -978,17 +944,11 @@
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="11" t="n"/>
       <c r="O16" s="5" t="n"/>
-      <c r="P16" s="12">
-        <f>IF(AND(L16="",N16=""),"",N(N16)-N(L16))</f>
-        <v/>
-      </c>
+      <c r="P16" s="12" t="n"/>
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="7" t="n"/>
       <c r="S16" s="5" t="n"/>
-      <c r="T16" s="13">
-        <f>IF(OR(P16="",R16=""),"",INT(ROUND(P16*R16,6)))</f>
-        <v/>
-      </c>
+      <c r="T16" s="13" t="n"/>
       <c r="U16" s="5" t="n"/>
       <c r="V16" s="5" t="n"/>
       <c r="W16" s="10" t="n"/>
@@ -1010,17 +970,11 @@
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="5" t="n"/>
-      <c r="P17" s="12">
-        <f>IF(AND(L17="",N17=""),"",N(N17)-N(L17))</f>
-        <v/>
-      </c>
+      <c r="P17" s="12" t="n"/>
       <c r="Q17" s="5" t="n"/>
       <c r="R17" s="7" t="n"/>
       <c r="S17" s="5" t="n"/>
-      <c r="T17" s="13">
-        <f>IF(OR(P17="",R17=""),"",INT(ROUND(P17*R17,6)))</f>
-        <v/>
-      </c>
+      <c r="T17" s="13" t="n"/>
       <c r="U17" s="5" t="n"/>
       <c r="V17" s="5" t="n"/>
       <c r="W17" s="10" t="n"/>
@@ -1042,17 +996,11 @@
       <c r="M18" s="5" t="n"/>
       <c r="N18" s="11" t="n"/>
       <c r="O18" s="5" t="n"/>
-      <c r="P18" s="12">
-        <f>IF(AND(L18="",N18=""),"",N(N18)-N(L18))</f>
-        <v/>
-      </c>
+      <c r="P18" s="12" t="n"/>
       <c r="Q18" s="5" t="n"/>
       <c r="R18" s="7" t="n"/>
       <c r="S18" s="5" t="n"/>
-      <c r="T18" s="13">
-        <f>IF(OR(P18="",R18=""),"",INT(ROUND(P18*R18,6)))</f>
-        <v/>
-      </c>
+      <c r="T18" s="13" t="n"/>
       <c r="U18" s="5" t="n"/>
       <c r="V18" s="5" t="n"/>
       <c r="W18" s="10" t="n"/>
@@ -1074,17 +1022,11 @@
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="11" t="n"/>
       <c r="O19" s="5" t="n"/>
-      <c r="P19" s="12">
-        <f>IF(AND(L19="",N19=""),"",N(N19)-N(L19))</f>
-        <v/>
-      </c>
+      <c r="P19" s="12" t="n"/>
       <c r="Q19" s="5" t="n"/>
       <c r="R19" s="7" t="n"/>
       <c r="S19" s="5" t="n"/>
-      <c r="T19" s="13">
-        <f>IF(OR(P19="",R19=""),"",INT(ROUND(P19*R19,6)))</f>
-        <v/>
-      </c>
+      <c r="T19" s="13" t="n"/>
       <c r="U19" s="5" t="n"/>
       <c r="V19" s="5" t="n"/>
       <c r="W19" s="10" t="n"/>
@@ -1106,17 +1048,11 @@
       <c r="M20" s="5" t="n"/>
       <c r="N20" s="11" t="n"/>
       <c r="O20" s="5" t="n"/>
-      <c r="P20" s="12">
-        <f>IF(AND(L20="",N20=""),"",N(N20)-N(L20))</f>
-        <v/>
-      </c>
+      <c r="P20" s="12" t="n"/>
       <c r="Q20" s="5" t="n"/>
       <c r="R20" s="7" t="n"/>
       <c r="S20" s="5" t="n"/>
-      <c r="T20" s="13">
-        <f>IF(OR(P20="",R20=""),"",INT(ROUND(P20*R20,6)))</f>
-        <v/>
-      </c>
+      <c r="T20" s="13" t="n"/>
       <c r="U20" s="5" t="n"/>
       <c r="V20" s="5" t="n"/>
       <c r="W20" s="10" t="n"/>
@@ -1138,17 +1074,11 @@
       <c r="M21" s="5" t="n"/>
       <c r="N21" s="11" t="n"/>
       <c r="O21" s="5" t="n"/>
-      <c r="P21" s="12">
-        <f>IF(AND(L21="",N21=""),"",N(N21)-N(L21))</f>
-        <v/>
-      </c>
+      <c r="P21" s="12" t="n"/>
       <c r="Q21" s="5" t="n"/>
       <c r="R21" s="7" t="n"/>
       <c r="S21" s="5" t="n"/>
-      <c r="T21" s="13">
-        <f>IF(OR(P21="",R21=""),"",INT(ROUND(P21*R21,6)))</f>
-        <v/>
-      </c>
+      <c r="T21" s="13" t="n"/>
       <c r="U21" s="5" t="n"/>
       <c r="V21" s="5" t="n"/>
       <c r="W21" s="10" t="n"/>
@@ -1170,17 +1100,11 @@
       <c r="M22" s="5" t="n"/>
       <c r="N22" s="11" t="n"/>
       <c r="O22" s="5" t="n"/>
-      <c r="P22" s="12">
-        <f>IF(AND(L22="",N22=""),"",N(N22)-N(L22))</f>
-        <v/>
-      </c>
+      <c r="P22" s="12" t="n"/>
       <c r="Q22" s="5" t="n"/>
       <c r="R22" s="7" t="n"/>
       <c r="S22" s="5" t="n"/>
-      <c r="T22" s="13">
-        <f>IF(OR(P22="",R22=""),"",INT(ROUND(P22*R22,6)))</f>
-        <v/>
-      </c>
+      <c r="T22" s="13" t="n"/>
       <c r="U22" s="5" t="n"/>
       <c r="V22" s="5" t="n"/>
       <c r="W22" s="10" t="n"/>
@@ -1202,17 +1126,11 @@
       <c r="M23" s="5" t="n"/>
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="5" t="n"/>
-      <c r="P23" s="12">
-        <f>IF(AND(L23="",N23=""),"",N(N23)-N(L23))</f>
-        <v/>
-      </c>
+      <c r="P23" s="12" t="n"/>
       <c r="Q23" s="5" t="n"/>
       <c r="R23" s="7" t="n"/>
       <c r="S23" s="5" t="n"/>
-      <c r="T23" s="13">
-        <f>IF(OR(P23="",R23=""),"",INT(ROUND(P23*R23,6)))</f>
-        <v/>
-      </c>
+      <c r="T23" s="13" t="n"/>
       <c r="U23" s="5" t="n"/>
       <c r="V23" s="5" t="n"/>
       <c r="W23" s="10" t="n"/>
@@ -1234,17 +1152,11 @@
       <c r="M24" s="5" t="n"/>
       <c r="N24" s="11" t="n"/>
       <c r="O24" s="5" t="n"/>
-      <c r="P24" s="12">
-        <f>IF(AND(L24="",N24=""),"",N(N24)-N(L24))</f>
-        <v/>
-      </c>
+      <c r="P24" s="12" t="n"/>
       <c r="Q24" s="5" t="n"/>
       <c r="R24" s="7" t="n"/>
       <c r="S24" s="5" t="n"/>
-      <c r="T24" s="13">
-        <f>IF(OR(P24="",R24=""),"",INT(ROUND(P24*R24,6)))</f>
-        <v/>
-      </c>
+      <c r="T24" s="13" t="n"/>
       <c r="U24" s="5" t="n"/>
       <c r="V24" s="5" t="n"/>
       <c r="W24" s="10" t="n"/>
@@ -1266,17 +1178,11 @@
       <c r="M25" s="5" t="n"/>
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="5" t="n"/>
-      <c r="P25" s="12">
-        <f>IF(AND(L25="",N25=""),"",N(N25)-N(L25))</f>
-        <v/>
-      </c>
+      <c r="P25" s="12" t="n"/>
       <c r="Q25" s="5" t="n"/>
       <c r="R25" s="7" t="n"/>
       <c r="S25" s="5" t="n"/>
-      <c r="T25" s="13">
-        <f>IF(OR(P25="",R25=""),"",INT(ROUND(P25*R25,6)))</f>
-        <v/>
-      </c>
+      <c r="T25" s="13" t="n"/>
       <c r="U25" s="5" t="n"/>
       <c r="V25" s="5" t="n"/>
       <c r="W25" s="10" t="n"/>
@@ -1298,17 +1204,11 @@
       <c r="M26" s="5" t="n"/>
       <c r="N26" s="11" t="n"/>
       <c r="O26" s="5" t="n"/>
-      <c r="P26" s="12">
-        <f>IF(AND(L26="",N26=""),"",N(N26)-N(L26))</f>
-        <v/>
-      </c>
+      <c r="P26" s="12" t="n"/>
       <c r="Q26" s="5" t="n"/>
       <c r="R26" s="7" t="n"/>
       <c r="S26" s="5" t="n"/>
-      <c r="T26" s="13">
-        <f>IF(OR(P26="",R26=""),"",INT(ROUND(P26*R26,6)))</f>
-        <v/>
-      </c>
+      <c r="T26" s="13" t="n"/>
       <c r="U26" s="5" t="n"/>
       <c r="V26" s="5" t="n"/>
       <c r="W26" s="10" t="n"/>
@@ -1334,10 +1234,7 @@
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="13">
-        <f>SUMIF(T13:T26,"&gt;0")</f>
-        <v/>
-      </c>
+      <c r="G30" s="13" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
@@ -1367,10 +1264,7 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="13">
-        <f>SUMIF(T13:T26,"&lt;0")</f>
-        <v/>
-      </c>
+      <c r="G31" s="13" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
@@ -1400,10 +1294,7 @@
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
-      <c r="G32" s="13">
-        <f>SUM(T13:T26)</f>
-        <v/>
-      </c>
+      <c r="G32" s="13" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
@@ -1490,6 +1381,7 @@
       </c>
     </row>
     <row r="39" ht="6" customHeight="1"/>
+    <row r="40"/>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
@@ -1700,1300 +1592,6 @@
     <mergeCell ref="W13:X13"/>
     <mergeCell ref="J17:K17"/>
   </mergeCells>
-  <conditionalFormatting sqref="L13:L26">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(L13),MOD(L13,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:N26">
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>AND(ISNUMBER(N13),MOD(N13,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P13:P26">
-    <cfRule type="expression" priority="3" dxfId="1">
-      <formula>AND(ISNUMBER(P13),MOD(P13,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="A13 A14 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"증가,감소,신규,협의"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>설계변경 산출내역서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계약번호</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>제2026-0312호</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  변경 차수</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>제1회</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계약금액</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="7" t="n">
-        <v>963241000</v>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  예정가격</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="7" t="n">
-        <v>1101487000</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  낙 찰 률</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="8">
-        <f>IF(N(G9)=0,"",G8/G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="6" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>공종·품명</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>규격</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>당초수량</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>변경수량</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="9" t="inlineStr">
-        <is>
-          <t>증감수량</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>적용단가</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="9" t="inlineStr">
-        <is>
-          <t>증감금액</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>단가 근거</t>
-        </is>
-      </c>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>증가</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>PE 이중벽관</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>D600</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="11" t="n">
-        <v>820</v>
-      </c>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="11" t="n">
-        <v>862</v>
-      </c>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="12">
-        <f>IF(AND(L13="",N13=""),"",N(N13)-N(L13))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="7" t="n">
-        <v>163090</v>
-      </c>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="13">
-        <f>IF(OR(P13="",R13=""),"",INT(ROUND(P13*R13,6)))</f>
-        <v/>
-      </c>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="10" t="inlineStr">
-        <is>
-          <t>계약단가</t>
-        </is>
-      </c>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>감소</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>아스팔트 포장(표층)</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>t=5cm</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="11" t="n">
-        <v>6300</v>
-      </c>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="11" t="n">
-        <v>6020</v>
-      </c>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="12">
-        <f>IF(AND(L14="",N14=""),"",N(N14)-N(L14))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="7" t="n">
-        <v>12480</v>
-      </c>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="13">
-        <f>IF(OR(P14="",R14=""),"",INT(ROUND(P14*R14,6)))</f>
-        <v/>
-      </c>
-      <c r="U14" s="5" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="10" t="inlineStr">
-        <is>
-          <t>계약단가</t>
-        </is>
-      </c>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>집수정</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>1.2×1.2</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>개소</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="12">
-        <f>IF(AND(L15="",N15=""),"",N(N15)-N(L15))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="7" t="n">
-        <v>1088777</v>
-      </c>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="13">
-        <f>IF(OR(P15="",R15=""),"",INT(ROUND(P15*R15,6)))</f>
-        <v/>
-      </c>
-      <c r="U15" s="5" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="10" t="inlineStr">
-        <is>
-          <t>당시단가×낙찰률</t>
-        </is>
-      </c>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>협의</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>가물막이(톤마대)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>1톤</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="12">
-        <f>IF(AND(L16="",N16=""),"",N(N16)-N(L16))</f>
-        <v/>
-      </c>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="7" t="n">
-        <v>36000</v>
-      </c>
-      <c r="S16" s="5" t="n"/>
-      <c r="T16" s="13">
-        <f>IF(OR(P16="",R16=""),"",INT(ROUND(P16*R16,6)))</f>
-        <v/>
-      </c>
-      <c r="U16" s="5" t="n"/>
-      <c r="V16" s="5" t="n"/>
-      <c r="W16" s="10" t="inlineStr">
-        <is>
-          <t>협의</t>
-        </is>
-      </c>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="12">
-        <f>IF(AND(L17="",N17=""),"",N(N17)-N(L17))</f>
-        <v/>
-      </c>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="7" t="n"/>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="13">
-        <f>IF(OR(P17="",R17=""),"",INT(ROUND(P17*R17,6)))</f>
-        <v/>
-      </c>
-      <c r="U17" s="5" t="n"/>
-      <c r="V17" s="5" t="n"/>
-      <c r="W17" s="10" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="11" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="12">
-        <f>IF(AND(L18="",N18=""),"",N(N18)-N(L18))</f>
-        <v/>
-      </c>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="7" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="13">
-        <f>IF(OR(P18="",R18=""),"",INT(ROUND(P18*R18,6)))</f>
-        <v/>
-      </c>
-      <c r="U18" s="5" t="n"/>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="10" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="11" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="12">
-        <f>IF(AND(L19="",N19=""),"",N(N19)-N(L19))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="7" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="13">
-        <f>IF(OR(P19="",R19=""),"",INT(ROUND(P19*R19,6)))</f>
-        <v/>
-      </c>
-      <c r="U19" s="5" t="n"/>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="10" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="11" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="12">
-        <f>IF(AND(L20="",N20=""),"",N(N20)-N(L20))</f>
-        <v/>
-      </c>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="7" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="13">
-        <f>IF(OR(P20="",R20=""),"",INT(ROUND(P20*R20,6)))</f>
-        <v/>
-      </c>
-      <c r="U20" s="5" t="n"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="10" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="12">
-        <f>IF(AND(L21="",N21=""),"",N(N21)-N(L21))</f>
-        <v/>
-      </c>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="7" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="13">
-        <f>IF(OR(P21="",R21=""),"",INT(ROUND(P21*R21,6)))</f>
-        <v/>
-      </c>
-      <c r="U21" s="5" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="10" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="11" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="11" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="12">
-        <f>IF(AND(L22="",N22=""),"",N(N22)-N(L22))</f>
-        <v/>
-      </c>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="7" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="13">
-        <f>IF(OR(P22="",R22=""),"",INT(ROUND(P22*R22,6)))</f>
-        <v/>
-      </c>
-      <c r="U22" s="5" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="10" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="10" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="12">
-        <f>IF(AND(L23="",N23=""),"",N(N23)-N(L23))</f>
-        <v/>
-      </c>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="7" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="13">
-        <f>IF(OR(P23="",R23=""),"",INT(ROUND(P23*R23,6)))</f>
-        <v/>
-      </c>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="10" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="10" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="12">
-        <f>IF(AND(L24="",N24=""),"",N(N24)-N(L24))</f>
-        <v/>
-      </c>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="7" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="13">
-        <f>IF(OR(P24="",R24=""),"",INT(ROUND(P24*R24,6)))</f>
-        <v/>
-      </c>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="10" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="12">
-        <f>IF(AND(L25="",N25=""),"",N(N25)-N(L25))</f>
-        <v/>
-      </c>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="7" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="13">
-        <f>IF(OR(P25="",R25=""),"",INT(ROUND(P25*R25,6)))</f>
-        <v/>
-      </c>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="10" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="10" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="11" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="12">
-        <f>IF(AND(L26="",N26=""),"",N(N26)-N(L26))</f>
-        <v/>
-      </c>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="7" t="n"/>
-      <c r="S26" s="5" t="n"/>
-      <c r="T26" s="13">
-        <f>IF(OR(P26="",R26=""),"",INT(ROUND(P26*R26,6)))</f>
-        <v/>
-      </c>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="10" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>※ 구분: 증가(계약단가) / 감소(계약단가) / 신규(설계변경 당시 단가 × 낙찰률) / 협의(발주기관 요구)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  증가 소계</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="13">
-        <f>SUMIF(T13:T26,"&gt;0")</f>
-        <v/>
-      </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="5" t="n"/>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="5" t="n"/>
-      <c r="T30" s="5" t="n"/>
-      <c r="U30" s="5" t="n"/>
-      <c r="V30" s="5" t="n"/>
-      <c r="W30" s="5" t="n"/>
-      <c r="X30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  감소 소계</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="13">
-        <f>SUMIF(T13:T26,"&lt;0")</f>
-        <v/>
-      </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="5" t="n"/>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" s="5" t="n"/>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="5" t="n"/>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="5" t="n"/>
-      <c r="X31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  증감 합계</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="13">
-        <f>SUM(T13:T26)</f>
-        <v/>
-      </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="5" t="n"/>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" s="5" t="n"/>
-      <c r="T32" s="5" t="n"/>
-      <c r="U32" s="5" t="n"/>
-      <c r="V32" s="5" t="n"/>
-      <c r="W32" s="5" t="n"/>
-      <c r="X32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  변경 후 계약금액</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="7" t="n">
-        <v>1011891000</v>
-      </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="5" t="n"/>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="5" t="n"/>
-      <c r="T33" s="5" t="n"/>
-      <c r="U33" s="5" t="n"/>
-      <c r="V33" s="5" t="n"/>
-      <c r="W33" s="5" t="n"/>
-      <c r="X33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="6" customHeight="1"/>
-    <row r="35" ht="10" customHeight="1"/>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="15" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="16" t="inlineStr"/>
-      <c r="K37" s="17" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q37" s="18" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U37" s="19" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="16" t="inlineStr"/>
-      <c r="K38" s="17" t="inlineStr">
-        <is>
-          <t>대표자</t>
-        </is>
-      </c>
-      <c r="Q38" s="18" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U38" s="19" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="6" customHeight="1"/>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="184">
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="G10:X10"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="W24:X24"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="U38:X38"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="T22:V22"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="K38:P38"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G31:X31"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="T20:V20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="T26:V26"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="G33:X33"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="T19:V19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="K37:P37"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A28:X28"/>
-    <mergeCell ref="G8:X8"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="Q38:T38"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="A41:X41"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="T21:V21"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="T23:V23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="W21:X21"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="T25:V25"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="G30:X30"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="G32:X32"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="A36:X36"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="J17:K17"/>
-  </mergeCells>
-  <conditionalFormatting sqref="L13:L26">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(L13),MOD(L13,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13:N26">
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>AND(ISNUMBER(N13),MOD(N13,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P13:P26">
-    <cfRule type="expression" priority="3" dxfId="1">
-      <formula>AND(ISNUMBER(P13),MOD(P13,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="A13 A14 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
       <formula1>"증가,감소,신규,협의"</formula1>

--- a/web/public/forms/chg-naeyeok.xlsx
+++ b/web/public/forms/chg-naeyeok.xlsx
@@ -585,7 +585,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
